--- a/data/figures/phase2/phase2_metrics.xlsx
+++ b/data/figures/phase2/phase2_metrics.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="26" uniqueCount="26">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="29" uniqueCount="29">
   <si>
     <t>mean_reachF</t>
   </si>
@@ -88,10 +88,19 @@
     <t>refractory M4: Hetero</t>
   </si>
   <si>
+    <t>M4: Hetero M5: Spatial</t>
+  </si>
+  <si>
     <t>async refractory misclass M4: Hetero</t>
   </si>
   <si>
+    <t>refractory misclass M4: Hetero M5: Spatial</t>
+  </si>
+  <si>
     <t>async refractory misclass M4: Hetero M5: Spatial</t>
+  </si>
+  <si>
+    <t>async refractory misclass M4: Hetero M5: Spatial async refractory misclass M4: Hetero M5: Spatial</t>
   </si>
 </sst>
 </file>
@@ -449,7 +458,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:S8"/>
+  <dimension ref="A1:S11"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:19">
@@ -516,58 +525,58 @@
         <v>19</v>
       </c>
       <c r="B2">
-        <v>64.598</v>
+        <v>64.114</v>
       </c>
       <c r="C2">
-        <v>6.253</v>
+        <v>6.676</v>
       </c>
       <c r="D2">
-        <v>24</v>
+        <v>50</v>
       </c>
       <c r="E2">
-        <v>99.988</v>
+        <v>99.986</v>
       </c>
       <c r="F2">
-        <v>0.057</v>
+        <v>0.073</v>
       </c>
       <c r="G2">
-        <v>24</v>
+        <v>50</v>
       </c>
       <c r="H2">
-        <v>480.6</v>
+        <v>493.196</v>
       </c>
       <c r="I2">
-        <v>142.099</v>
+        <v>129.168</v>
       </c>
       <c r="J2">
-        <v>20</v>
+        <v>46</v>
       </c>
       <c r="K2">
-        <v>2128.45</v>
+        <v>2126.696</v>
       </c>
       <c r="L2">
-        <v>27.773</v>
+        <v>22.553</v>
       </c>
       <c r="M2">
-        <v>20</v>
+        <v>46</v>
       </c>
       <c r="N2">
-        <v>24.6</v>
+        <v>25.283</v>
       </c>
       <c r="O2">
-        <v>3.455</v>
+        <v>3.462</v>
       </c>
       <c r="P2">
-        <v>20</v>
+        <v>46</v>
       </c>
       <c r="Q2">
-        <v>57.75</v>
+        <v>57.717</v>
       </c>
       <c r="R2">
-        <v>1.293</v>
+        <v>1.846</v>
       </c>
       <c r="S2">
-        <v>20</v>
+        <v>46</v>
       </c>
     </row>
     <row r="3" spans="1:19">
@@ -575,58 +584,58 @@
         <v>20</v>
       </c>
       <c r="B3">
-        <v>62.763</v>
+        <v>63.288</v>
       </c>
       <c r="C3">
-        <v>7.898</v>
+        <v>6.82</v>
       </c>
       <c r="D3">
-        <v>40</v>
+        <v>63</v>
       </c>
       <c r="E3">
-        <v>100</v>
+        <v>99.84999999999999</v>
       </c>
       <c r="F3">
-        <v>0</v>
+        <v>0.509</v>
       </c>
       <c r="G3">
-        <v>40</v>
+        <v>63</v>
       </c>
       <c r="H3">
-        <v>511.675</v>
+        <v>495.635</v>
       </c>
       <c r="I3">
-        <v>131.752</v>
+        <v>129.762</v>
       </c>
       <c r="J3">
-        <v>40</v>
+        <v>63</v>
       </c>
       <c r="K3">
-        <v>2104.45</v>
+        <v>2057.54</v>
       </c>
       <c r="L3">
-        <v>28.802</v>
+        <v>69.402</v>
       </c>
       <c r="M3">
-        <v>40</v>
+        <v>63</v>
       </c>
       <c r="N3">
-        <v>24.375</v>
+        <v>26.175</v>
       </c>
       <c r="O3">
-        <v>3.143</v>
+        <v>4.546</v>
       </c>
       <c r="P3">
-        <v>40</v>
+        <v>63</v>
       </c>
       <c r="Q3">
-        <v>57.175</v>
+        <v>57.683</v>
       </c>
       <c r="R3">
-        <v>1.662</v>
+        <v>1.533</v>
       </c>
       <c r="S3">
-        <v>40</v>
+        <v>63</v>
       </c>
     </row>
     <row r="4" spans="1:19">
@@ -811,55 +820,55 @@
         <v>24</v>
       </c>
       <c r="B7">
-        <v>87.752</v>
+        <v>63.842</v>
       </c>
       <c r="C7">
-        <v>2.262</v>
+        <v>6.193</v>
       </c>
       <c r="D7">
         <v>20</v>
       </c>
       <c r="E7">
-        <v>100</v>
+        <v>99.63200000000001</v>
       </c>
       <c r="F7">
-        <v>0</v>
+        <v>0.944</v>
       </c>
       <c r="G7">
         <v>20</v>
       </c>
       <c r="H7">
-        <v>621.75</v>
+        <v>488.25</v>
       </c>
       <c r="I7">
-        <v>87.55800000000001</v>
+        <v>99.343</v>
       </c>
       <c r="J7">
         <v>20</v>
       </c>
       <c r="K7">
-        <v>2303.55</v>
+        <v>1973.05</v>
       </c>
       <c r="L7">
-        <v>23.874</v>
+        <v>53.988</v>
       </c>
       <c r="M7">
         <v>20</v>
       </c>
       <c r="N7">
-        <v>25.7</v>
+        <v>29.2</v>
       </c>
       <c r="O7">
-        <v>2.273</v>
+        <v>3.222</v>
       </c>
       <c r="P7">
         <v>20</v>
       </c>
       <c r="Q7">
-        <v>58.75</v>
+        <v>58.65</v>
       </c>
       <c r="R7">
-        <v>0.444</v>
+        <v>0.745</v>
       </c>
       <c r="S7">
         <v>20</v>
@@ -870,10 +879,10 @@
         <v>25</v>
       </c>
       <c r="B8">
-        <v>87.676</v>
+        <v>87.752</v>
       </c>
       <c r="C8">
-        <v>2.494</v>
+        <v>2.262</v>
       </c>
       <c r="D8">
         <v>20</v>
@@ -888,39 +897,216 @@
         <v>20</v>
       </c>
       <c r="H8">
+        <v>621.75</v>
+      </c>
+      <c r="I8">
+        <v>87.55800000000001</v>
+      </c>
+      <c r="J8">
+        <v>20</v>
+      </c>
+      <c r="K8">
+        <v>2303.55</v>
+      </c>
+      <c r="L8">
+        <v>23.874</v>
+      </c>
+      <c r="M8">
+        <v>20</v>
+      </c>
+      <c r="N8">
+        <v>25.7</v>
+      </c>
+      <c r="O8">
+        <v>2.273</v>
+      </c>
+      <c r="P8">
+        <v>20</v>
+      </c>
+      <c r="Q8">
+        <v>58.75</v>
+      </c>
+      <c r="R8">
+        <v>0.444</v>
+      </c>
+      <c r="S8">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="9" spans="1:19">
+      <c r="A9" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="B9">
+        <v>83.56</v>
+      </c>
+      <c r="C9">
+        <v>1.061</v>
+      </c>
+      <c r="D9">
+        <v>3</v>
+      </c>
+      <c r="E9">
+        <v>99.773</v>
+      </c>
+      <c r="F9">
+        <v>0.359</v>
+      </c>
+      <c r="G9">
+        <v>3</v>
+      </c>
+      <c r="H9">
+        <v>475.333</v>
+      </c>
+      <c r="I9">
+        <v>61.849</v>
+      </c>
+      <c r="J9">
+        <v>3</v>
+      </c>
+      <c r="K9">
+        <v>2155.333</v>
+      </c>
+      <c r="L9">
+        <v>73.711</v>
+      </c>
+      <c r="M9">
+        <v>3</v>
+      </c>
+      <c r="N9">
+        <v>34</v>
+      </c>
+      <c r="O9">
+        <v>3.606</v>
+      </c>
+      <c r="P9">
+        <v>3</v>
+      </c>
+      <c r="Q9">
+        <v>59</v>
+      </c>
+      <c r="R9">
+        <v>0</v>
+      </c>
+      <c r="S9">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="10" spans="1:19">
+      <c r="A10" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="B10">
+        <v>87.676</v>
+      </c>
+      <c r="C10">
+        <v>2.494</v>
+      </c>
+      <c r="D10">
+        <v>20</v>
+      </c>
+      <c r="E10">
+        <v>100</v>
+      </c>
+      <c r="F10">
+        <v>0</v>
+      </c>
+      <c r="G10">
+        <v>20</v>
+      </c>
+      <c r="H10">
         <v>610.3</v>
       </c>
-      <c r="I8">
+      <c r="I10">
         <v>102.259</v>
       </c>
-      <c r="J8">
-        <v>20</v>
-      </c>
-      <c r="K8">
+      <c r="J10">
+        <v>20</v>
+      </c>
+      <c r="K10">
         <v>2306.05</v>
       </c>
-      <c r="L8">
+      <c r="L10">
         <v>18.698</v>
       </c>
-      <c r="M8">
-        <v>20</v>
-      </c>
-      <c r="N8">
+      <c r="M10">
+        <v>20</v>
+      </c>
+      <c r="N10">
         <v>24.8</v>
       </c>
-      <c r="O8">
+      <c r="O10">
         <v>1.765</v>
       </c>
-      <c r="P8">
-        <v>20</v>
-      </c>
-      <c r="Q8">
+      <c r="P10">
+        <v>20</v>
+      </c>
+      <c r="Q10">
         <v>58.7</v>
       </c>
-      <c r="R8">
+      <c r="R10">
         <v>0.571</v>
       </c>
-      <c r="S8">
+      <c r="S10">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="11" spans="1:19">
+      <c r="A11" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="B11">
+        <v>86.01000000000001</v>
+      </c>
+      <c r="C11">
+        <v>3.517</v>
+      </c>
+      <c r="D11">
+        <v>20</v>
+      </c>
+      <c r="E11">
+        <v>99.964</v>
+      </c>
+      <c r="F11">
+        <v>0.094</v>
+      </c>
+      <c r="G11">
+        <v>20</v>
+      </c>
+      <c r="H11">
+        <v>537.6</v>
+      </c>
+      <c r="I11">
+        <v>91.175</v>
+      </c>
+      <c r="J11">
+        <v>20</v>
+      </c>
+      <c r="K11">
+        <v>2215.25</v>
+      </c>
+      <c r="L11">
+        <v>51.058</v>
+      </c>
+      <c r="M11">
+        <v>20</v>
+      </c>
+      <c r="N11">
+        <v>28.75</v>
+      </c>
+      <c r="O11">
+        <v>2.789</v>
+      </c>
+      <c r="P11">
+        <v>20</v>
+      </c>
+      <c r="Q11">
+        <v>58.75</v>
+      </c>
+      <c r="R11">
+        <v>0.55</v>
+      </c>
+      <c r="S11">
         <v>20</v>
       </c>
     </row>

--- a/data/figures/phase2/phase2_metrics.xlsx
+++ b/data/figures/phase2/phase2_metrics.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="29" uniqueCount="29">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="26" uniqueCount="26">
   <si>
     <t>mean_reachF</t>
   </si>
@@ -70,37 +70,28 @@
     <t>n_t_peak_r</t>
   </si>
   <si>
+    <t>cond</t>
+  </si>
+  <si>
     <t>Condition</t>
   </si>
   <si>
-    <t>M4: Hetero</t>
-  </si>
-  <si>
-    <t>M5: Spatial</t>
-  </si>
-  <si>
-    <t>async M4: Hetero</t>
-  </si>
-  <si>
-    <t>misclass M4: Hetero</t>
-  </si>
-  <si>
-    <t>refractory M4: Hetero</t>
-  </si>
-  <si>
-    <t>M4: Hetero M5: Spatial</t>
-  </si>
-  <si>
-    <t>async refractory misclass M4: Hetero</t>
-  </si>
-  <si>
-    <t>refractory misclass M4: Hetero M5: Spatial</t>
-  </si>
-  <si>
-    <t>async refractory misclass M4: Hetero M5: Spatial</t>
-  </si>
-  <si>
-    <t>async refractory misclass M4: Hetero M5: Spatial async refractory misclass M4: Hetero M5: Spatial</t>
+    <t>HET</t>
+  </si>
+  <si>
+    <t>SPA</t>
+  </si>
+  <si>
+    <t>HET+SPA</t>
+  </si>
+  <si>
+    <t>het</t>
+  </si>
+  <si>
+    <t>spa</t>
+  </si>
+  <si>
+    <t>het_spa</t>
   </si>
 </sst>
 </file>
@@ -458,12 +449,12 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:S11"/>
+  <dimension ref="A1:T4"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
-    <row r="1" spans="1:19">
+    <row r="1" spans="1:20">
       <c r="A1" s="1" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="B1" s="1" t="s">
         <v>0</v>
@@ -519,595 +510,194 @@
       <c r="S1" s="1" t="s">
         <v>17</v>
       </c>
+      <c r="T1" s="1" t="s">
+        <v>18</v>
+      </c>
     </row>
-    <row r="2" spans="1:19">
+    <row r="2" spans="1:20">
       <c r="A2" s="1" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="B2">
-        <v>64.114</v>
+        <v>62.662</v>
       </c>
       <c r="C2">
-        <v>6.676</v>
+        <v>6.738</v>
       </c>
       <c r="D2">
-        <v>50</v>
+        <v>40</v>
       </c>
       <c r="E2">
-        <v>99.986</v>
+        <v>99.66</v>
       </c>
       <c r="F2">
-        <v>0.073</v>
+        <v>0.923</v>
       </c>
       <c r="G2">
-        <v>50</v>
+        <v>40</v>
       </c>
       <c r="H2">
-        <v>493.196</v>
+        <v>452.8</v>
       </c>
       <c r="I2">
-        <v>129.168</v>
+        <v>132.157</v>
       </c>
       <c r="J2">
-        <v>46</v>
+        <v>40</v>
       </c>
       <c r="K2">
-        <v>2126.696</v>
+        <v>2043.3</v>
       </c>
       <c r="L2">
-        <v>22.553</v>
+        <v>90.121</v>
       </c>
       <c r="M2">
-        <v>46</v>
+        <v>40</v>
       </c>
       <c r="N2">
-        <v>25.283</v>
+        <v>26.775</v>
       </c>
       <c r="O2">
-        <v>3.462</v>
+        <v>3.301</v>
       </c>
       <c r="P2">
-        <v>46</v>
+        <v>40</v>
       </c>
       <c r="Q2">
-        <v>57.717</v>
+        <v>58.075</v>
       </c>
       <c r="R2">
-        <v>1.846</v>
+        <v>1.685</v>
       </c>
       <c r="S2">
-        <v>46</v>
+        <v>40</v>
+      </c>
+      <c r="T2" t="s">
+        <v>23</v>
       </c>
     </row>
-    <row r="3" spans="1:19">
+    <row r="3" spans="1:20">
       <c r="A3" s="1" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="B3">
-        <v>63.288</v>
+        <v>60.754</v>
       </c>
       <c r="C3">
-        <v>6.82</v>
+        <v>5.868</v>
       </c>
       <c r="D3">
-        <v>63</v>
+        <v>20</v>
       </c>
       <c r="E3">
-        <v>99.84999999999999</v>
+        <v>99.148</v>
       </c>
       <c r="F3">
-        <v>0.509</v>
+        <v>1.547</v>
       </c>
       <c r="G3">
-        <v>63</v>
+        <v>20</v>
       </c>
       <c r="H3">
-        <v>495.635</v>
+        <v>427.4</v>
       </c>
       <c r="I3">
-        <v>129.762</v>
+        <v>102.482</v>
       </c>
       <c r="J3">
-        <v>63</v>
+        <v>20</v>
       </c>
       <c r="K3">
-        <v>2057.54</v>
+        <v>1971</v>
       </c>
       <c r="L3">
-        <v>69.402</v>
+        <v>74.795</v>
       </c>
       <c r="M3">
-        <v>63</v>
+        <v>20</v>
       </c>
       <c r="N3">
-        <v>26.175</v>
+        <v>29.15</v>
       </c>
       <c r="O3">
-        <v>4.546</v>
+        <v>4.246</v>
       </c>
       <c r="P3">
-        <v>63</v>
+        <v>20</v>
       </c>
       <c r="Q3">
-        <v>57.683</v>
+        <v>58.6</v>
       </c>
       <c r="R3">
-        <v>1.533</v>
+        <v>0.883</v>
       </c>
       <c r="S3">
-        <v>63</v>
+        <v>20</v>
+      </c>
+      <c r="T3" t="s">
+        <v>24</v>
       </c>
     </row>
-    <row r="4" spans="1:19">
+    <row r="4" spans="1:20">
       <c r="A4" s="1" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="B4">
-        <v>63.8</v>
+        <v>61.284</v>
       </c>
       <c r="C4">
-        <v>6.748</v>
+        <v>5.382</v>
       </c>
       <c r="D4">
         <v>20</v>
       </c>
       <c r="E4">
-        <v>100</v>
+        <v>99.322</v>
       </c>
       <c r="F4">
-        <v>0</v>
+        <v>1.228</v>
       </c>
       <c r="G4">
         <v>20</v>
       </c>
       <c r="H4">
-        <v>496.95</v>
+        <v>439.1</v>
       </c>
       <c r="I4">
-        <v>110.524</v>
+        <v>112.852</v>
       </c>
       <c r="J4">
         <v>20</v>
       </c>
       <c r="K4">
-        <v>2159.3</v>
+        <v>1964.7</v>
       </c>
       <c r="L4">
-        <v>13.083</v>
+        <v>52.158</v>
       </c>
       <c r="M4">
         <v>20</v>
       </c>
       <c r="N4">
-        <v>20.65</v>
+        <v>28.25</v>
       </c>
       <c r="O4">
-        <v>2.961</v>
+        <v>2.789</v>
       </c>
       <c r="P4">
         <v>20</v>
       </c>
       <c r="Q4">
-        <v>56.05</v>
+        <v>58.75</v>
       </c>
       <c r="R4">
-        <v>3.471</v>
+        <v>0.444</v>
       </c>
       <c r="S4">
         <v>20</v>
       </c>
-    </row>
-    <row r="5" spans="1:19">
-      <c r="A5" s="1" t="s">
-        <v>22</v>
-      </c>
-      <c r="B5">
-        <v>79.506</v>
-      </c>
-      <c r="C5">
-        <v>4.977</v>
-      </c>
-      <c r="D5">
-        <v>20</v>
-      </c>
-      <c r="E5">
-        <v>99.97</v>
-      </c>
-      <c r="F5">
-        <v>0.074</v>
-      </c>
-      <c r="G5">
-        <v>20</v>
-      </c>
-      <c r="H5">
-        <v>183.6</v>
-      </c>
-      <c r="I5">
-        <v>41.826</v>
-      </c>
-      <c r="J5">
-        <v>20</v>
-      </c>
-      <c r="K5">
-        <v>2137.15</v>
-      </c>
-      <c r="L5">
-        <v>20.866</v>
-      </c>
-      <c r="M5">
-        <v>20</v>
-      </c>
-      <c r="N5">
-        <v>15.8</v>
-      </c>
-      <c r="O5">
-        <v>1.508</v>
-      </c>
-      <c r="P5">
-        <v>20</v>
-      </c>
-      <c r="Q5">
-        <v>56.8</v>
-      </c>
-      <c r="R5">
-        <v>2.118</v>
-      </c>
-      <c r="S5">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="6" spans="1:19">
-      <c r="A6" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="B6">
-        <v>69.378</v>
-      </c>
-      <c r="C6">
-        <v>4.656</v>
-      </c>
-      <c r="D6">
-        <v>20</v>
-      </c>
-      <c r="E6">
-        <v>93.614</v>
-      </c>
-      <c r="F6">
-        <v>3.901</v>
-      </c>
-      <c r="G6">
-        <v>20</v>
-      </c>
-      <c r="H6">
-        <v>976.55</v>
-      </c>
-      <c r="I6">
-        <v>121.48</v>
-      </c>
-      <c r="J6">
-        <v>20</v>
-      </c>
-      <c r="K6">
-        <v>1920.3</v>
-      </c>
-      <c r="L6">
-        <v>129.469</v>
-      </c>
-      <c r="M6">
-        <v>20</v>
-      </c>
-      <c r="N6">
-        <v>34.5</v>
-      </c>
-      <c r="O6">
-        <v>2.646</v>
-      </c>
-      <c r="P6">
-        <v>20</v>
-      </c>
-      <c r="Q6">
-        <v>59</v>
-      </c>
-      <c r="R6">
-        <v>0</v>
-      </c>
-      <c r="S6">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="7" spans="1:19">
-      <c r="A7" s="1" t="s">
-        <v>24</v>
-      </c>
-      <c r="B7">
-        <v>63.842</v>
-      </c>
-      <c r="C7">
-        <v>6.193</v>
-      </c>
-      <c r="D7">
-        <v>20</v>
-      </c>
-      <c r="E7">
-        <v>99.63200000000001</v>
-      </c>
-      <c r="F7">
-        <v>0.944</v>
-      </c>
-      <c r="G7">
-        <v>20</v>
-      </c>
-      <c r="H7">
-        <v>488.25</v>
-      </c>
-      <c r="I7">
-        <v>99.343</v>
-      </c>
-      <c r="J7">
-        <v>20</v>
-      </c>
-      <c r="K7">
-        <v>1973.05</v>
-      </c>
-      <c r="L7">
-        <v>53.988</v>
-      </c>
-      <c r="M7">
-        <v>20</v>
-      </c>
-      <c r="N7">
-        <v>29.2</v>
-      </c>
-      <c r="O7">
-        <v>3.222</v>
-      </c>
-      <c r="P7">
-        <v>20</v>
-      </c>
-      <c r="Q7">
-        <v>58.65</v>
-      </c>
-      <c r="R7">
-        <v>0.745</v>
-      </c>
-      <c r="S7">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="8" spans="1:19">
-      <c r="A8" s="1" t="s">
+      <c r="T4" t="s">
         <v>25</v>
-      </c>
-      <c r="B8">
-        <v>87.752</v>
-      </c>
-      <c r="C8">
-        <v>2.262</v>
-      </c>
-      <c r="D8">
-        <v>20</v>
-      </c>
-      <c r="E8">
-        <v>100</v>
-      </c>
-      <c r="F8">
-        <v>0</v>
-      </c>
-      <c r="G8">
-        <v>20</v>
-      </c>
-      <c r="H8">
-        <v>621.75</v>
-      </c>
-      <c r="I8">
-        <v>87.55800000000001</v>
-      </c>
-      <c r="J8">
-        <v>20</v>
-      </c>
-      <c r="K8">
-        <v>2303.55</v>
-      </c>
-      <c r="L8">
-        <v>23.874</v>
-      </c>
-      <c r="M8">
-        <v>20</v>
-      </c>
-      <c r="N8">
-        <v>25.7</v>
-      </c>
-      <c r="O8">
-        <v>2.273</v>
-      </c>
-      <c r="P8">
-        <v>20</v>
-      </c>
-      <c r="Q8">
-        <v>58.75</v>
-      </c>
-      <c r="R8">
-        <v>0.444</v>
-      </c>
-      <c r="S8">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="9" spans="1:19">
-      <c r="A9" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="B9">
-        <v>83.56</v>
-      </c>
-      <c r="C9">
-        <v>1.061</v>
-      </c>
-      <c r="D9">
-        <v>3</v>
-      </c>
-      <c r="E9">
-        <v>99.773</v>
-      </c>
-      <c r="F9">
-        <v>0.359</v>
-      </c>
-      <c r="G9">
-        <v>3</v>
-      </c>
-      <c r="H9">
-        <v>475.333</v>
-      </c>
-      <c r="I9">
-        <v>61.849</v>
-      </c>
-      <c r="J9">
-        <v>3</v>
-      </c>
-      <c r="K9">
-        <v>2155.333</v>
-      </c>
-      <c r="L9">
-        <v>73.711</v>
-      </c>
-      <c r="M9">
-        <v>3</v>
-      </c>
-      <c r="N9">
-        <v>34</v>
-      </c>
-      <c r="O9">
-        <v>3.606</v>
-      </c>
-      <c r="P9">
-        <v>3</v>
-      </c>
-      <c r="Q9">
-        <v>59</v>
-      </c>
-      <c r="R9">
-        <v>0</v>
-      </c>
-      <c r="S9">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="10" spans="1:19">
-      <c r="A10" s="1" t="s">
-        <v>27</v>
-      </c>
-      <c r="B10">
-        <v>87.676</v>
-      </c>
-      <c r="C10">
-        <v>2.494</v>
-      </c>
-      <c r="D10">
-        <v>20</v>
-      </c>
-      <c r="E10">
-        <v>100</v>
-      </c>
-      <c r="F10">
-        <v>0</v>
-      </c>
-      <c r="G10">
-        <v>20</v>
-      </c>
-      <c r="H10">
-        <v>610.3</v>
-      </c>
-      <c r="I10">
-        <v>102.259</v>
-      </c>
-      <c r="J10">
-        <v>20</v>
-      </c>
-      <c r="K10">
-        <v>2306.05</v>
-      </c>
-      <c r="L10">
-        <v>18.698</v>
-      </c>
-      <c r="M10">
-        <v>20</v>
-      </c>
-      <c r="N10">
-        <v>24.8</v>
-      </c>
-      <c r="O10">
-        <v>1.765</v>
-      </c>
-      <c r="P10">
-        <v>20</v>
-      </c>
-      <c r="Q10">
-        <v>58.7</v>
-      </c>
-      <c r="R10">
-        <v>0.571</v>
-      </c>
-      <c r="S10">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="11" spans="1:19">
-      <c r="A11" s="1" t="s">
-        <v>28</v>
-      </c>
-      <c r="B11">
-        <v>86.01000000000001</v>
-      </c>
-      <c r="C11">
-        <v>3.517</v>
-      </c>
-      <c r="D11">
-        <v>20</v>
-      </c>
-      <c r="E11">
-        <v>99.964</v>
-      </c>
-      <c r="F11">
-        <v>0.094</v>
-      </c>
-      <c r="G11">
-        <v>20</v>
-      </c>
-      <c r="H11">
-        <v>537.6</v>
-      </c>
-      <c r="I11">
-        <v>91.175</v>
-      </c>
-      <c r="J11">
-        <v>20</v>
-      </c>
-      <c r="K11">
-        <v>2215.25</v>
-      </c>
-      <c r="L11">
-        <v>51.058</v>
-      </c>
-      <c r="M11">
-        <v>20</v>
-      </c>
-      <c r="N11">
-        <v>28.75</v>
-      </c>
-      <c r="O11">
-        <v>2.789</v>
-      </c>
-      <c r="P11">
-        <v>20</v>
-      </c>
-      <c r="Q11">
-        <v>58.75</v>
-      </c>
-      <c r="R11">
-        <v>0.55</v>
-      </c>
-      <c r="S11">
-        <v>20</v>
       </c>
     </row>
   </sheetData>
